--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/15_industry_context_patterns.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/15_industry_context_patterns.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R24b353357a75409f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rca7ef6487e2a4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R9095e197934948ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rc7401a13bd604ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rc0776557ea8749c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R5d30a9e60ee247cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R11084e0a0fd34648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R3675ec73c4204559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R133c93d0d4b34c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6bc6689716ad48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rfd02d046707f4e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Ra1dc6f50a1104ce1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -618,7 +618,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4e09921e3104db8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72f002605b6d41fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -749,7 +749,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J6" s="78" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -784,7 +784,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J7" s="79" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K7" s="45" t="str">
         <x:v>High</x:v>
@@ -819,7 +819,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>High</x:v>
@@ -854,7 +854,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>High</x:v>
@@ -889,7 +889,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>High</x:v>
@@ -924,7 +924,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>Medium</x:v>
@@ -959,7 +959,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>High</x:v>
@@ -994,7 +994,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>High</x:v>
@@ -1029,7 +1029,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>High</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K15" t="str">
         <x:v>High</x:v>
@@ -1099,7 +1099,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K16" t="str">
         <x:v>Medium</x:v>
@@ -1134,7 +1134,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K17" t="str">
         <x:v>High</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K18" t="str">
         <x:v>High</x:v>
@@ -1204,7 +1204,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K19" t="str">
         <x:v>High</x:v>
@@ -1239,7 +1239,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K20" t="str">
         <x:v>High</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K21" t="str">
         <x:v>Medium</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K22" t="str">
         <x:v>High</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Attach client evidence for selected record (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K23" t="str">
         <x:v>High</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Reconcile selected record (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K24" t="str">
         <x:v>High</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K25" t="str">
         <x:v>High</x:v>
@@ -1449,7 +1449,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Validate selected record (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for industry context patterns.</x:v>
       </x:c>
       <x:c r="K26" t="str">
         <x:v>Medium</x:v>
@@ -1484,7 +1484,7 @@
         <x:v>AbarVa synthetic industry pattern library</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Validate with client-specific operating model and evidence.</x:v>
+        <x:v>Confirm selected record (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this industry context patterns record is used downstream.</x:v>
       </x:c>
       <x:c r="K27" t="str">
         <x:v>High</x:v>
@@ -1508,7 +1508,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd815362af3614f2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477d6b95237c4043"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1583,7 +1583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R077b32869b104817"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27ecdf8968844605"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1727,7 +1727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cc1b2372fc64288"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2dd70410284104"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1797,7 +1797,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84d40b5f2d7d4bf5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47eda2f6c7b34953"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1907,7 +1907,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295a5982a7ad4913"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eb83e0e97804da4"/>
   </x:tableParts>
 </x:worksheet>
 </file>